--- a/Utetruck1.xlsx
+++ b/Utetruck1.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedometic-my.sharepoint.com/personal/martin_petersson_dometic_com/Documents/Skrivbordet/HOME1/Apps/Frekvensanalys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A6FECB2-81DA-4766-8C00-C3441003D84F}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4952B0ED-1FF3-49F2-85CA-3C402F6A6374}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Kategori</t>
   </si>
@@ -44,62 +47,122 @@
     <t>Aktivitet</t>
   </si>
   <si>
-    <t>Möten</t>
+    <t>Lastning</t>
   </si>
   <si>
     <t>Övrigt</t>
   </si>
   <si>
-    <t>Processarbete</t>
-  </si>
-  <si>
-    <t>Kör emballage</t>
-  </si>
-  <si>
-    <t>Kör material borr</t>
-  </si>
-  <si>
-    <t>Kör material flöde</t>
-  </si>
-  <si>
-    <t>Utan truck</t>
-  </si>
-  <si>
     <t>Rast</t>
   </si>
   <si>
-    <t>Lastning</t>
-  </si>
-  <si>
-    <t>Avlastning</t>
-  </si>
-  <si>
-    <t>Flytta material från 60</t>
-  </si>
-  <si>
-    <t>Flytta material från fabrik</t>
-  </si>
-  <si>
-    <t>Lastning från 60</t>
-  </si>
-  <si>
-    <t>Lastning 43</t>
-  </si>
-  <si>
-    <t>Avlastning 43</t>
-  </si>
-  <si>
-    <t>Avlastning 60</t>
-  </si>
-  <si>
-    <t>Avlastning till godsmottagning</t>
+    <t>Morgonmöte</t>
+  </si>
+  <si>
+    <t>Gång</t>
+  </si>
+  <si>
+    <t>Pålastning</t>
+  </si>
+  <si>
+    <t>Flytta pallar</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Prata i telefon</t>
+  </si>
+  <si>
+    <t>Kolla listor</t>
+  </si>
+  <si>
+    <t>Lämna papper på kontor</t>
+  </si>
+  <si>
+    <t>Hämta papper på kontor</t>
+  </si>
+  <si>
+    <t>Flytta material-60</t>
+  </si>
+  <si>
+    <t>Flytta material-43</t>
+  </si>
+  <si>
+    <t>Flytta verktyg-60</t>
+  </si>
+  <si>
+    <t>Flytta material-124</t>
+  </si>
+  <si>
+    <t>Flytta avfall-60</t>
+  </si>
+  <si>
+    <t>Flytta avfall-43</t>
+  </si>
+  <si>
+    <t>Tomkörning-60</t>
+  </si>
+  <si>
+    <t>Tomkörning-43</t>
+  </si>
+  <si>
+    <t>Tomkörning-124</t>
+  </si>
+  <si>
+    <t>Flytta verktyg-43</t>
+  </si>
+  <si>
+    <t>Flytta verktyg-124</t>
+  </si>
+  <si>
+    <t>Flytta avfall-124</t>
+  </si>
+  <si>
+    <t>Tomkörning-lastning</t>
+  </si>
+  <si>
+    <t>Lossning</t>
+  </si>
+  <si>
+    <t>Tomkörning-lossning</t>
+  </si>
+  <si>
+    <t>Inlagring</t>
+  </si>
+  <si>
+    <t>Från 60</t>
+  </si>
+  <si>
+    <t>Från 43</t>
+  </si>
+  <si>
+    <t>Från 124</t>
+  </si>
+  <si>
+    <t>Flytta produkter-60</t>
+  </si>
+  <si>
+    <t>Flytta produkter-43</t>
+  </si>
+  <si>
+    <t>Flytta produkter-124</t>
+  </si>
+  <si>
+    <t>Köra tompall</t>
+  </si>
+  <si>
+    <t>Utanför truck-lastning</t>
+  </si>
+  <si>
+    <t>Utanför truck-lossning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +178,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,6 +234,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -265,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -287,6 +362,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,9 +524,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C25" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:C25" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C32" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A1:C32" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A3768F14-CCAD-44BA-BF45-88778F5F665B}" name="Kategori" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{C4189BEF-9E3C-4B91-9321-6CBA1D620671}" name="Underkategori" dataDxfId="4"/>
@@ -749,20 +830,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" customWidth="1"/>
-    <col min="8" max="9" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="30.453125" customWidth="1"/>
+    <col min="8" max="9" width="17.54296875" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -773,245 +854,353 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="10"/>
-    </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+    <row r="31" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="12"/>
-    </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="12"/>
-    </row>
-    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="12"/>
-    </row>
-    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    </row>
+    <row r="32" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B32" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="14"/>
-    </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="14"/>
-    </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="14"/>
-    </row>
-    <row r="25" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>10</v>
+      <c r="C32" s="14" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C29:C1048576 C1">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C36:C1048576 C1">
     <cfRule type="duplicateValues" dxfId="2" priority="294"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C1048576">
+  <conditionalFormatting sqref="C36:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="296"/>
     <cfRule type="duplicateValues" dxfId="0" priority="298"/>
   </conditionalFormatting>

--- a/Utetruck1.xlsx
+++ b/Utetruck1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedometic-my.sharepoint.com/personal/martin_petersson_dometic_com/Documents/Skrivbordet/HOME1/Apps/Frekvensanalys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4952B0ED-1FF3-49F2-85CA-3C402F6A6374}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="8_{5B1E7E70-6A2C-4FA5-9913-59E9EA794D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A29648D3-0A8E-4FF1-BE4C-56AA7EABD7ED}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="43">
   <si>
     <t>Kategori</t>
   </si>
@@ -62,12 +62,6 @@
     <t>Gång</t>
   </si>
   <si>
-    <t>Pålastning</t>
-  </si>
-  <si>
-    <t>Flytta pallar</t>
-  </si>
-  <si>
     <t>Administration</t>
   </si>
   <si>
@@ -95,12 +89,6 @@
     <t>Flytta material-124</t>
   </si>
   <si>
-    <t>Flytta avfall-60</t>
-  </si>
-  <si>
-    <t>Flytta avfall-43</t>
-  </si>
-  <si>
     <t>Tomkörning-60</t>
   </si>
   <si>
@@ -116,21 +104,9 @@
     <t>Flytta verktyg-124</t>
   </si>
   <si>
-    <t>Flytta avfall-124</t>
-  </si>
-  <si>
-    <t>Tomkörning-lastning</t>
-  </si>
-  <si>
     <t>Lossning</t>
   </si>
   <si>
-    <t>Tomkörning-lossning</t>
-  </si>
-  <si>
-    <t>Inlagring</t>
-  </si>
-  <si>
     <t>Från 60</t>
   </si>
   <si>
@@ -156,6 +132,39 @@
   </si>
   <si>
     <t>Utanför truck-lossning</t>
+  </si>
+  <si>
+    <t>Förbereda för lastning</t>
+  </si>
+  <si>
+    <t>Transport från lossning</t>
+  </si>
+  <si>
+    <t>Tömma container-60</t>
+  </si>
+  <si>
+    <t>Tömma container-43</t>
+  </si>
+  <si>
+    <t>Tömma container-124</t>
+  </si>
+  <si>
+    <t>Tömma bana-60</t>
+  </si>
+  <si>
+    <t>Tömma bana-43</t>
+  </si>
+  <si>
+    <t>Hjälpa underhåll</t>
+  </si>
+  <si>
+    <t>Från underhåll</t>
+  </si>
+  <si>
+    <t>Flytta verktyg-underhåll</t>
+  </si>
+  <si>
+    <t>Tomkörning-underhåll</t>
   </si>
 </sst>
 </file>
@@ -185,7 +194,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,6 +249,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -340,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -364,6 +379,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,8 +546,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C32" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
-  <autoFilter ref="A1:C32" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}" name="Table1" displayName="Table1" ref="A1:C36" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A1:C36" xr:uid="{BF48DA23-3E59-4607-B2B4-8A642AED3858}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A3768F14-CCAD-44BA-BF45-88778F5F665B}" name="Kategori" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{C4189BEF-9E3C-4B91-9321-6CBA1D620671}" name="Underkategori" dataDxfId="4"/>
@@ -830,7 +847,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
@@ -862,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -873,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -884,81 +901,81 @@
         <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>38</v>
+      <c r="A5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>30</v>
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>39</v>
+      <c r="A9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>17</v>
@@ -966,211 +983,211 @@
     </row>
     <row r="12" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>19</v>
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>11</v>
+      <c r="A25" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>12</v>
+      <c r="A26" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>7</v>
+    </row>
+    <row r="29" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1181,10 +1198,10 @@
         <v>4</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>4</v>
       </c>
@@ -1192,15 +1209,59 @@
         <v>4</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>37</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C36:C1048576 C1">
+  <conditionalFormatting sqref="C39:C1048576 C1">
     <cfRule type="duplicateValues" dxfId="2" priority="294"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:C1048576">
+  <conditionalFormatting sqref="C39:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="296"/>
     <cfRule type="duplicateValues" dxfId="0" priority="298"/>
   </conditionalFormatting>
